--- a/backlog/product_backlog.xlsx
+++ b/backlog/product_backlog.xlsx
@@ -47,7 +47,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -55,19 +55,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -511,7 +505,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="100" customHeight="1">
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>US-00</t>
@@ -519,12 +513,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>User Registration and Login</t>
+          <t>Account Registration and Login</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>As any user (TA applicant, module organiser, or admin), I want to register an account and log in to the system so that I can access role-specific features and maintain my personal data securely.</t>
+          <t>As a system user (TA applicant, module organiser, or admin), I want to access the system through secure account login so that I can use features based on my role.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -537,11 +531,11 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1.User can register with student/staff ID, password, and select role;
-2.Required fields (ID, password, role) are validated; ID format is checked;
-3.User can log in with registered ID and password;
-4.System identifies user role after login and redirects to role-specific dashboard;
-5.User can log out and session is terminated; all modified content is stored.</t>
+          <t>1.TA applicant can register with student ID and password;
+2.Staff/admin can log in with pre-created accounts;
+3.Required fields and ID format are validated and duplicate IDs are rejected;
+4.User can log in with correct credentials and is redirected to a role-specific dashboard;
+5.User can log out and the session is terminated.</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
@@ -559,7 +553,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="54" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>US-01</t>
@@ -572,7 +566,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>As a TA applicant, I want to create my personal profile so that I can show my personal information when applying for suitable jobs.</t>
+          <t>As a TA applicant, I want to create my personal profile so that I can present relevant information when applying for jobs.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -585,9 +579,9 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1.User can enter name, age, gender, education, expected salary, and desired positions;
+          <t>1.Applicant can enter name, student ID, programme/major, year of study, education level, skills, available time slots, and desired positions;
 2.Required fields are validated;
-3.Profile is saved successfully.</t>
+3.Profile is saved and linked to the applicant account.</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
@@ -605,7 +599,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="4" ht="58" customHeight="1">
+    <row r="4" ht="54" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>US-02</t>
@@ -651,7 +645,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="5" ht="72" customHeight="1">
+    <row r="5" ht="54" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>US-03</t>
@@ -697,7 +691,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="6" ht="72" customHeight="1">
+    <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>US-04</t>
@@ -745,7 +739,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="7" ht="43" customHeight="1">
+    <row r="7" ht="54" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>US-05</t>
@@ -791,7 +785,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>US-06</t>
@@ -837,7 +831,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="9" ht="58" customHeight="1">
+    <row r="9" ht="43" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>US-07</t>
@@ -882,7 +876,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="10" ht="72" customHeight="1">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>US-08</t>
@@ -928,7 +922,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
+    <row r="11" ht="54" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>US-09</t>
@@ -974,7 +968,7 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
+    <row r="12" ht="54" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>US-10</t>
@@ -1020,7 +1014,7 @@
         <v>46157</v>
       </c>
     </row>
-    <row r="13" ht="72" customHeight="1">
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>US-11</t>
@@ -1066,7 +1060,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="14" ht="72" customHeight="1">
+    <row r="14" ht="54" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>US-12</t>
@@ -1112,7 +1106,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
+    <row r="15" ht="72" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>US-13</t>
@@ -1149,7 +1143,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Core feature; merged from Review Applications and Shortlist/Select stories</t>
+          <t>Core feature</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
@@ -1159,7 +1153,7 @@
         <v>46125</v>
       </c>
     </row>
-    <row r="16" ht="58" customHeight="1">
+    <row r="16" ht="54" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>US-14</t>
@@ -1191,7 +1185,7 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1205,7 +1199,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="17" ht="100" customHeight="1">
+    <row r="17" ht="72" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>US-15</t>
@@ -1242,7 +1236,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Mandatory function; depends on US-11 (schedule data) and US-14 (workload data)</t>
+          <t>Mandatory function; depends on US-11 and US-14</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1252,7 +1246,6 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="18" ht="100" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
